--- a/data/Gender index data/2014-2023_Index_World_economic_forum.xlsx
+++ b/data/Gender index data/2014-2023_Index_World_economic_forum.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giuliodamico/Documents/GitHub/Gender-Inequality-Index-vs-Female-jail-population/notebooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giuliodamico/Documents/GitHub/Gender-Inequality-Index-vs-Female-jail-population/data/Gender index data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464F09C9-D176-BD49-9F81-F0B195126A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAD80C2-30DC-2849-A018-B66C8A9FB38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="29400" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -193,9 +193,6 @@
     <t>0.787</t>
   </si>
   <si>
-    <t>Uk</t>
-  </si>
-  <si>
     <t>0.7383</t>
   </si>
   <si>
@@ -211,9 +208,6 @@
     <t>0.774</t>
   </si>
   <si>
-    <t>Bulgary</t>
-  </si>
-  <si>
     <t>0.7444</t>
   </si>
   <si>
@@ -238,9 +232,6 @@
     <t>0.785</t>
   </si>
   <si>
-    <t>Lituania</t>
-  </si>
-  <si>
     <t>0.7208</t>
   </si>
   <si>
@@ -256,9 +247,6 @@
     <t>0.745</t>
   </si>
   <si>
-    <t>Netherland</t>
-  </si>
-  <si>
     <t>0.7730</t>
   </si>
   <si>
@@ -313,9 +301,6 @@
     <t>0.734</t>
   </si>
   <si>
-    <t>Albany</t>
-  </si>
-  <si>
     <t>0.6869</t>
   </si>
   <si>
@@ -418,9 +403,6 @@
     <t>0.712</t>
   </si>
   <si>
-    <t>Louxemburg</t>
-  </si>
-  <si>
     <t>0.7333</t>
   </si>
   <si>
@@ -445,9 +427,6 @@
     <t>0.724</t>
   </si>
   <si>
-    <t>Ukrain</t>
-  </si>
-  <si>
     <t>0.7056</t>
   </si>
   <si>
@@ -457,9 +436,6 @@
     <t>0.721</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>0.6943</t>
   </si>
   <si>
@@ -508,18 +484,12 @@
     <t>0.680</t>
   </si>
   <si>
-    <t>slovakia</t>
-  </si>
-  <si>
     <t>0.6806</t>
   </si>
   <si>
     <t>0.694</t>
   </si>
   <si>
-    <t>Czech Rep.</t>
-  </si>
-  <si>
     <t>0.6737</t>
   </si>
   <si>
@@ -598,13 +568,43 @@
     <t>0.635</t>
   </si>
   <si>
-    <t>bosnia</t>
-  </si>
-  <si>
     <t>0.675</t>
   </si>
   <si>
     <t>0.679</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
+    <t>Czech Republic</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina</t>
   </si>
 </sst>
 </file>
@@ -1319,22 +1319,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>57</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>58</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>59</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>60</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
       </c>
       <c r="H11" t="s">
         <v>48</v>
@@ -1351,25 +1351,25 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>63</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>64</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" t="s">
         <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" t="s">
-        <v>67</v>
       </c>
       <c r="I12">
         <v>0.746</v>
@@ -1383,13 +1383,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
         <v>68</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
       </c>
       <c r="D13" t="s">
         <v>50</v>
@@ -1415,25 +1415,25 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
         <v>71</v>
       </c>
-      <c r="B14" t="s">
+      <c r="F14" t="s">
         <v>72</v>
       </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="H14" t="s">
         <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" t="s">
-        <v>76</v>
       </c>
       <c r="I14">
         <v>0.80400000000000005</v>
@@ -1447,25 +1447,25 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I15">
         <v>0.76200000000000001</v>
@@ -1479,25 +1479,25 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" t="s">
         <v>82</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" t="s">
-        <v>86</v>
       </c>
       <c r="I16">
         <v>0.78800000000000003</v>
@@ -1511,25 +1511,25 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" t="s">
         <v>87</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" t="s">
-        <v>91</v>
       </c>
       <c r="I17">
         <v>0.78900000000000003</v>
@@ -1543,25 +1543,25 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I18">
         <v>0.73299999999999998</v>
@@ -1575,25 +1575,25 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" t="s">
         <v>96</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F19" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" t="s">
-        <v>101</v>
       </c>
       <c r="I19">
         <v>0.77</v>
@@ -1607,25 +1607,25 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" t="s">
         <v>102</v>
-      </c>
-      <c r="B20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" t="s">
-        <v>107</v>
       </c>
       <c r="I20">
         <v>0.76800000000000002</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I21">
         <v>0.77500000000000002</v>
@@ -1671,25 +1671,25 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" t="s">
         <v>111</v>
-      </c>
-      <c r="B22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>114</v>
-      </c>
-      <c r="F22" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" t="s">
-        <v>116</v>
       </c>
       <c r="I22">
         <v>0.78</v>
@@ -1703,25 +1703,25 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I23">
         <v>0.71299999999999997</v>
@@ -1735,25 +1735,25 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I24">
         <v>0.77700000000000002</v>
@@ -1767,25 +1767,25 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" t="s">
         <v>125</v>
       </c>
-      <c r="B25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" t="s">
-        <v>129</v>
-      </c>
-      <c r="F25" t="s">
-        <v>130</v>
-      </c>
       <c r="H25" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I25">
         <v>0.73299999999999998</v>
@@ -1799,25 +1799,25 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H26" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I26">
         <v>0.72599999999999998</v>
@@ -1831,25 +1831,25 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I27">
         <v>0.7</v>
@@ -1863,25 +1863,25 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F28" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I28">
         <v>0.71399999999999997</v>
@@ -1895,25 +1895,25 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I29">
         <v>0.71499999999999997</v>
@@ -1927,25 +1927,25 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H30" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I30">
         <v>0.73199999999999998</v>
@@ -1959,25 +1959,25 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H31" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I31">
         <v>0.72099999999999997</v>
@@ -1991,25 +1991,25 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F32" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H32" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I32">
         <v>0.68899999999999995</v>
@@ -2023,25 +2023,25 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="F33" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H33" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I33">
         <v>0.71199999999999997</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C34" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F34" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H34" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I34">
         <v>0.71099999999999997</v>
@@ -2087,25 +2087,25 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F35" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="H35" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I35">
         <v>0.70299999999999996</v>
@@ -2119,25 +2119,25 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E36" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F36" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="H36" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I36">
         <v>0.70699999999999996</v>
@@ -2151,25 +2151,25 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F37" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H37" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I37">
         <v>0.68799999999999994</v>
@@ -2183,25 +2183,25 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C38" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F38" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="H38" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I38">
         <v>0.63800000000000001</v>
@@ -2215,19 +2215,19 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F39" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H39" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I39">
         <v>0.71299999999999997</v>

--- a/data/Gender index data/2014-2023_Index_World_economic_forum.xlsx
+++ b/data/Gender index data/2014-2023_Index_World_economic_forum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giuliodamico/Documents/GitHub/Gender-Inequality-Index-vs-Female-jail-population/data/Gender index data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAADC29F-15FA-9345-B24F-6BB9159304EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32325B3D-F41C-F549-9C76-30C2C31EBA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,13 +136,13 @@
     <t>North Macedonia</t>
   </si>
   <si>
-    <t>Czech Republic</t>
-  </si>
-  <si>
     <t>Bosnia and Herzegovina</t>
   </si>
   <si>
     <t>Latvia</t>
+  </si>
+  <si>
+    <t>Czechia</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34">
         <v>0.67369999999999997</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39">
         <v>0.68500000000000005</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40">
         <v>0.76910000000000001</v>
